--- a/dist/downloads/model-documents/openbmb-agentcpm-report.xlsx
+++ b/dist/downloads/model-documents/openbmb-agentcpm-report.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="Rb45f4427d13c419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="Rb2856792c66c4f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="Re75744a5cc9e41b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R90d51c798dcd410c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -3453,7 +3453,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -4649,7 +4649,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" hidden="0" customHeight="1">
@@ -5845,7 +5845,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
@@ -7041,7 +7041,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD71" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" hidden="0" customHeight="1">
@@ -8237,7 +8237,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD84" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="24" hidden="0" customHeight="1">
@@ -9433,7 +9433,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD97" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="24" hidden="0" customHeight="1">
@@ -10629,7 +10629,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD110" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="24" hidden="0" customHeight="1">
@@ -11825,7 +11825,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD123" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
@@ -13021,7 +13021,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD136" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="24" hidden="0" customHeight="1">
@@ -14217,7 +14217,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD149" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="24" hidden="0" customHeight="1">
@@ -15413,7 +15413,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD162" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="24" hidden="0" customHeight="1">
@@ -16609,7 +16609,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD175" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
@@ -17805,7 +17805,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD188" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="24" hidden="0" customHeight="1">
@@ -19001,7 +19001,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -20197,7 +20197,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD214" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="24" hidden="0" customHeight="1">
@@ -21393,7 +21393,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD227" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="24" hidden="0" customHeight="1">
@@ -22589,7 +22589,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD240" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="24" hidden="0" customHeight="1">
@@ -23785,7 +23785,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD253" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="24" hidden="0" customHeight="1">
@@ -24981,7 +24981,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD266" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="24" hidden="0" customHeight="1">
@@ -26177,7 +26177,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD279" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="24" hidden="0" customHeight="1">
@@ -27373,7 +27373,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD292" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="24" hidden="0" customHeight="1">
@@ -28569,7 +28569,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD305" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="24" hidden="0" customHeight="1">
@@ -29765,7 +29765,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD318" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="24" hidden="0" customHeight="1">
@@ -30961,7 +30961,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD331" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="24" hidden="0" customHeight="1">
@@ -32157,7 +32157,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD344" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="24" hidden="0" customHeight="1">
@@ -33353,7 +33353,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD357" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="24" hidden="0" customHeight="1">
@@ -34549,7 +34549,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD370" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="24" hidden="0" customHeight="1">
@@ -35745,7 +35745,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD383" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="24" hidden="0" customHeight="1">
@@ -36941,7 +36941,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD396" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="24" hidden="0" customHeight="1">
@@ -38137,7 +38137,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD409" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="410" ht="24" hidden="0" customHeight="1">
@@ -39123,7 +39123,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -39387,7 +39387,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -39400,7 +39403,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -40016,8 +40022,8 @@
       <x:c r="E70" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -40025,6 +40031,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
